--- a/sample_book.xlsx
+++ b/sample_book.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/20c40e0a7296ab97/ドキュメント/@KEC/01_VBA/Git_GitHub/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pct16\Documents\sample01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{4952FADE-568E-439E-80C8-DBCB46997AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72B2B253-51DA-409B-B437-3FF0C31312AF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC2DA359-D00C-40ED-8583-489AC758E8CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4785" yWindow="1920" windowWidth="21600" windowHeight="11295" xr2:uid="{BF225344-2B12-4909-8088-39360917B0CA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BF225344-2B12-4909-8088-39360917B0CA}"/>
   </bookViews>
   <sheets>
     <sheet name="記録" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t>年</t>
   </si>
@@ -92,6 +92,10 @@
     <rPh sb="10" eb="13">
       <t>ガクシュウヨウ</t>
     </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>ozaki</t>
     <phoneticPr fontId="5"/>
   </si>
 </sst>
@@ -193,7 +197,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -213,6 +217,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -233,9 +243,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -273,7 +283,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -379,7 +389,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -521,7 +531,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -530,27 +540,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1453D4A-DE5D-45B7-93F2-6FAC117EE4D2}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="3" max="3" width="10.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="6"/>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C2" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="6"/>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="C3" s="8">
+        <v>46170</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>10</v>
       </c>
+      <c r="C4" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5"/>
@@ -561,9 +576,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8777766-EDAE-456C-9180-36CBBA1C0181}">
   <dimension ref="B2"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>11</v>
       </c>
@@ -577,12 +592,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DE89EDC-D7E6-4653-A78F-C37A582A6F72}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="7" width="6.625" customWidth="1"/>
+    <col min="1" max="7" width="6.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -596,7 +611,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -619,7 +634,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="str">
         <f>_xlfn.LET(_xlpm.startDate,DATE($B$1,$D$1,1),_xlpm.firstDayOfWeek,WEEKDAY(_xlpm.startDate),_xlpm.dayNum,1-_xlpm.firstDayOfWeek+1,_xlpm.lastDay,DAY(EOMONTH(_xlpm.startDate,0)),IF(AND(_xlpm.dayNum&gt;=1,_xlpm.dayNum&lt;=_xlpm.lastDay),_xlpm.dayNum,""))</f>
         <v/>
@@ -649,7 +664,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" s="3">
         <f>_xlfn.LET(_xlpm.startDate,DATE($B$1,$D$1,1),_xlpm.firstDayOfWeek,WEEKDAY(_xlpm.startDate),_xlpm.dayNum,8-_xlpm.firstDayOfWeek+1,_xlpm.lastDay,DAY(EOMONTH(_xlpm.startDate,0)),IF(AND(_xlpm.dayNum&gt;=1,_xlpm.dayNum&lt;=_xlpm.lastDay),_xlpm.dayNum,""))</f>
         <v>3</v>
@@ -679,7 +694,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" s="3">
         <f>_xlfn.LET(_xlpm.startDate,DATE($B$1,$D$1,1),_xlpm.firstDayOfWeek,WEEKDAY(_xlpm.startDate),_xlpm.dayNum,15-_xlpm.firstDayOfWeek+1,_xlpm.lastDay,DAY(EOMONTH(_xlpm.startDate,0)),IF(AND(_xlpm.dayNum&gt;=1,_xlpm.dayNum&lt;=_xlpm.lastDay),_xlpm.dayNum,""))</f>
         <v>10</v>
@@ -709,7 +724,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A7" s="3">
         <f>_xlfn.LET(_xlpm.startDate,DATE($B$1,$D$1,1),_xlpm.firstDayOfWeek,WEEKDAY(_xlpm.startDate),_xlpm.dayNum,22-_xlpm.firstDayOfWeek+1,_xlpm.lastDay,DAY(EOMONTH(_xlpm.startDate,0)),IF(AND(_xlpm.dayNum&gt;=1,_xlpm.dayNum&lt;=_xlpm.lastDay),_xlpm.dayNum,""))</f>
         <v>17</v>
@@ -739,7 +754,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A8" s="3">
         <f>_xlfn.LET(_xlpm.startDate,DATE($B$1,$D$1,1),_xlpm.firstDayOfWeek,WEEKDAY(_xlpm.startDate),_xlpm.dayNum,29-_xlpm.firstDayOfWeek+1,_xlpm.lastDay,DAY(EOMONTH(_xlpm.startDate,0)),IF(AND(_xlpm.dayNum&gt;=1,_xlpm.dayNum&lt;=_xlpm.lastDay),_xlpm.dayNum,""))</f>
         <v>24</v>
@@ -769,7 +784,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A9" s="3">
         <f>_xlfn.LET(_xlpm.startDate,DATE($B$1,$D$1,1),_xlpm.firstDayOfWeek,WEEKDAY(_xlpm.startDate),_xlpm.dayNum,36-_xlpm.firstDayOfWeek+1,_xlpm.lastDay,DAY(EOMONTH(_xlpm.startDate,0)),IF(AND(_xlpm.dayNum&gt;=1,_xlpm.dayNum&lt;=_xlpm.lastDay),_xlpm.dayNum,""))</f>
         <v>31</v>
